--- a/healthcare_surveys/020_health_communication_equity_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/020_health_communication_equity_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,8 +715,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'print_newspaper'}</t>
+          <t>print_newspaper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Print Newspaper'}</t>
+          <t>Print Newspaper</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'television'}</t>
+          <t>television</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Television'}</t>
+          <t>Television</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_'radio'}</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 'Radio'}</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_7,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 7, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2-3_times_a_week'}</t>
+          <t>2-3_times_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2-3 times a week'}</t>
+          <t>2-3 times a week</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1_time_a_week'}</t>
+          <t>1_time_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1 time a week'}</t>
+          <t>1 time a week</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2_times_a_week'}</t>
+          <t>2_times_a_week</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2 times a week'}</t>
+          <t>2 times a week</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'1_time_a_month'}</t>
+          <t>1_time_a_month</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '1 time a month'}</t>
+          <t>1 time a month</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_'less_than_1_time_a_month'}</t>
+          <t>less_than_1_time_a_month</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 'Less than 1 time a month'}</t>
+          <t>Less than 1 time a month</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_7,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 7, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'american_indian/alaska_native'}</t>
+          <t>american_indian/alaska_native</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'American Indian/Alaska Native'}</t>
+          <t>American Indian/Alaska Native</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'native_hawaiian/pacific_islander'}</t>
+          <t>native_hawaiian/pacific_islander</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Native Hawaiian/Pacific Islander'}</t>
+          <t>Native Hawaiian/Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_'some_other_race/ethnicity'}</t>
+          <t>some_other_race/ethnicity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 'Some other race/ethnicity'}</t>
+          <t>Some other race/ethnicity</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_7,_'label':_'prefer_not_to_report'}</t>
+          <t>prefer_not_to_report</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 7, 'label': 'Prefer not to report'}</t>
+          <t>Prefer not to report</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
